--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1403508771929824</v>
+        <v>0.05833333333333333</v>
       </c>
       <c r="B2">
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2482269503546099</v>
+        <v>0.1408450704225352</v>
       </c>
       <c r="D2">
-        <v>0.8617886178861789</v>
+        <v>0.9457364341085271</v>
       </c>
       <c r="E2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>9</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.05833333333333333</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.1408450704225352</v>
+        <v>0.1690140845070423</v>
       </c>
       <c r="D2">
-        <v>0.9457364341085271</v>
+        <v>0.9076923076923077</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
